--- a/Martin County Football Spreadsheet.xlsx
+++ b/Martin County Football Spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cw216\Desktop\Martin County Football\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C397F2C2-A346-457D-BE9F-D7B930AD0931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A4A57F-032A-4E97-AEBA-0D2B4533A917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{EEE30F3B-AD82-4EEF-B45E-03C43AB7F1EC}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3065" uniqueCount="206">
   <si>
     <t>Year</t>
   </si>
@@ -654,12 +654,15 @@
   <si>
     <t>Teco Stadium</t>
   </si>
+  <si>
+    <t>Knox Central</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -716,8 +719,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -760,8 +778,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -910,11 +934,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1011,15 +1055,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1048,6 +1083,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1382,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667AF051-AB7B-436D-8B26-5AAD1AA83032}">
-  <dimension ref="A1:P487"/>
+  <dimension ref="A1:P570"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.26171875" customWidth="1"/>
@@ -20219,46 +20282,1643 @@
       <c r="P486" s="17"/>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A487" s="10">
+      <c r="A487" s="49">
         <v>2024</v>
       </c>
-      <c r="B487" s="11">
+      <c r="B487" s="50">
         <v>45983</v>
       </c>
-      <c r="C487" s="13" t="s">
+      <c r="C487" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="D487" s="13">
-        <v>7</v>
-      </c>
-      <c r="E487" s="13">
+      <c r="D487" s="51">
+        <v>7</v>
+      </c>
+      <c r="E487" s="51">
         <v>44</v>
       </c>
-      <c r="F487" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G487" s="13"/>
-      <c r="H487" s="13">
-        <v>1</v>
-      </c>
-      <c r="I487" s="13"/>
-      <c r="J487" s="13"/>
-      <c r="K487" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="L487" s="13" t="s">
+      <c r="F487" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G487" s="51"/>
+      <c r="H487" s="51">
+        <v>1</v>
+      </c>
+      <c r="I487" s="51"/>
+      <c r="J487" s="51"/>
+      <c r="K487" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="L487" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="M487" s="13" t="s">
+      <c r="M487" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="N487" s="13" t="s">
+      <c r="N487" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="O487" s="13" t="s">
+      <c r="O487" s="51" t="s">
         <v>194</v>
       </c>
       <c r="P487" s="21"/>
+    </row>
+    <row r="488" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A488" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B488" s="53">
+        <v>45891</v>
+      </c>
+      <c r="C488" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D488" s="54">
+        <v>7</v>
+      </c>
+      <c r="E488" s="54">
+        <v>35</v>
+      </c>
+      <c r="F488" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G488" s="54"/>
+      <c r="H488" s="54">
+        <v>1</v>
+      </c>
+      <c r="I488" s="54"/>
+      <c r="J488" s="54"/>
+      <c r="K488" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="L488" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="M488" s="54"/>
+      <c r="N488" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O488" s="54"/>
+    </row>
+    <row r="489" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A489" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B489" s="53">
+        <v>45898</v>
+      </c>
+      <c r="C489" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D489" s="54">
+        <v>44</v>
+      </c>
+      <c r="E489" s="54">
+        <v>20</v>
+      </c>
+      <c r="F489" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G489" s="54">
+        <v>1</v>
+      </c>
+      <c r="H489" s="54"/>
+      <c r="I489" s="54"/>
+      <c r="J489" s="54"/>
+      <c r="K489" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="L489" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="M489" s="54"/>
+      <c r="N489" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O489" s="54"/>
+    </row>
+    <row r="490" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A490" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B490" s="53">
+        <v>45905</v>
+      </c>
+      <c r="C490" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D490" s="54">
+        <v>48</v>
+      </c>
+      <c r="E490" s="54">
+        <v>18</v>
+      </c>
+      <c r="F490" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G490" s="54">
+        <v>1</v>
+      </c>
+      <c r="H490" s="54"/>
+      <c r="I490" s="54"/>
+      <c r="J490" s="54"/>
+      <c r="K490" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="L490" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="M490" s="54"/>
+      <c r="N490" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O490" s="54"/>
+    </row>
+    <row r="491" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A491" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B491" s="53">
+        <v>45912</v>
+      </c>
+      <c r="C491" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="D491" s="54">
+        <v>42</v>
+      </c>
+      <c r="E491" s="54">
+        <v>41</v>
+      </c>
+      <c r="F491" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G491" s="54">
+        <v>1</v>
+      </c>
+      <c r="H491" s="54"/>
+      <c r="I491" s="54"/>
+      <c r="J491" s="54"/>
+      <c r="K491" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="L491" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="M491" s="54"/>
+      <c r="N491" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O491" s="54"/>
+    </row>
+    <row r="492" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A492" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B492" s="53">
+        <v>45919</v>
+      </c>
+      <c r="C492" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="D492" s="54">
+        <v>40</v>
+      </c>
+      <c r="E492" s="54">
+        <v>20</v>
+      </c>
+      <c r="F492" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G492" s="54">
+        <v>1</v>
+      </c>
+      <c r="H492" s="54"/>
+      <c r="I492" s="54"/>
+      <c r="J492" s="54"/>
+      <c r="K492" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="L492" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="M492" s="54"/>
+      <c r="N492" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O492" s="54"/>
+    </row>
+    <row r="493" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A493" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B493" s="53">
+        <v>45926</v>
+      </c>
+      <c r="C493" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="D493" s="54">
+        <v>41</v>
+      </c>
+      <c r="E493" s="54">
+        <v>6</v>
+      </c>
+      <c r="F493" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G493" s="54">
+        <v>1</v>
+      </c>
+      <c r="H493" s="54"/>
+      <c r="I493" s="54"/>
+      <c r="J493" s="54"/>
+      <c r="K493" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="L493" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M493" s="54"/>
+      <c r="N493" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O493" s="54"/>
+    </row>
+    <row r="494" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A494" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B494" s="53">
+        <v>45933</v>
+      </c>
+      <c r="C494" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="D494" s="54">
+        <v>48</v>
+      </c>
+      <c r="E494" s="54">
+        <v>18</v>
+      </c>
+      <c r="F494" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G494" s="54">
+        <v>1</v>
+      </c>
+      <c r="H494" s="54"/>
+      <c r="I494" s="54"/>
+      <c r="J494" s="54"/>
+      <c r="K494" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="L494" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="M494" s="54"/>
+      <c r="N494" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O494" s="54"/>
+    </row>
+    <row r="495" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A495" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B495" s="53">
+        <v>45947</v>
+      </c>
+      <c r="C495" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D495" s="54">
+        <v>46</v>
+      </c>
+      <c r="E495" s="54">
+        <v>14</v>
+      </c>
+      <c r="F495" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G495" s="54">
+        <v>1</v>
+      </c>
+      <c r="H495" s="54"/>
+      <c r="I495" s="54"/>
+      <c r="J495" s="54"/>
+      <c r="K495" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="L495" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="M495" s="54"/>
+      <c r="N495" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O495" s="54"/>
+    </row>
+    <row r="496" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A496" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B496" s="53">
+        <v>45954</v>
+      </c>
+      <c r="C496" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="D496" s="54"/>
+      <c r="E496" s="54"/>
+      <c r="F496" s="54"/>
+      <c r="G496" s="54"/>
+      <c r="H496" s="54"/>
+      <c r="I496" s="54"/>
+      <c r="J496" s="54"/>
+      <c r="K496" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="L496" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="M496" s="54"/>
+      <c r="N496" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O496" s="54"/>
+    </row>
+    <row r="497" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A497" s="52">
+        <v>2025</v>
+      </c>
+      <c r="B497" s="53">
+        <v>45961</v>
+      </c>
+      <c r="C497" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D497" s="54"/>
+      <c r="E497" s="54"/>
+      <c r="F497" s="54"/>
+      <c r="G497" s="54"/>
+      <c r="H497" s="54"/>
+      <c r="I497" s="54"/>
+      <c r="J497" s="54"/>
+      <c r="K497" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="L497" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="M497" s="54"/>
+      <c r="N497" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O497" s="54"/>
+    </row>
+    <row r="498" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A498" s="55"/>
+      <c r="B498" s="55"/>
+      <c r="C498" s="55"/>
+      <c r="D498" s="55"/>
+      <c r="E498" s="55"/>
+      <c r="F498" s="55"/>
+      <c r="G498" s="55"/>
+      <c r="H498" s="55"/>
+      <c r="I498" s="55"/>
+      <c r="J498" s="55"/>
+      <c r="K498" s="55"/>
+      <c r="L498" s="55"/>
+      <c r="M498" s="55"/>
+      <c r="N498" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="O498" s="55"/>
+    </row>
+    <row r="499" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A499" s="55"/>
+      <c r="B499" s="55"/>
+      <c r="C499" s="55"/>
+      <c r="D499" s="55"/>
+      <c r="E499" s="55"/>
+      <c r="F499" s="55"/>
+      <c r="G499" s="55"/>
+      <c r="H499" s="55"/>
+      <c r="I499" s="55"/>
+      <c r="J499" s="55"/>
+      <c r="K499" s="55"/>
+      <c r="L499" s="55"/>
+      <c r="M499" s="55"/>
+      <c r="N499" s="55"/>
+      <c r="O499" s="55"/>
+    </row>
+    <row r="500" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A500" s="55"/>
+      <c r="B500" s="55"/>
+      <c r="C500" s="55"/>
+      <c r="D500" s="55"/>
+      <c r="E500" s="55"/>
+      <c r="F500" s="55"/>
+      <c r="G500" s="55"/>
+      <c r="H500" s="55"/>
+      <c r="I500" s="55"/>
+      <c r="J500" s="55"/>
+      <c r="K500" s="55"/>
+      <c r="L500" s="55"/>
+      <c r="M500" s="55"/>
+      <c r="N500" s="55"/>
+      <c r="O500" s="55"/>
+    </row>
+    <row r="501" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A501" s="55"/>
+      <c r="B501" s="55"/>
+      <c r="C501" s="55"/>
+      <c r="D501" s="55"/>
+      <c r="E501" s="55"/>
+      <c r="F501" s="55"/>
+      <c r="G501" s="55"/>
+      <c r="H501" s="55"/>
+      <c r="I501" s="55"/>
+      <c r="J501" s="55"/>
+      <c r="K501" s="55"/>
+      <c r="L501" s="55"/>
+      <c r="M501" s="55"/>
+      <c r="N501" s="55"/>
+      <c r="O501" s="55"/>
+    </row>
+    <row r="502" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A502" s="55"/>
+      <c r="B502" s="55"/>
+      <c r="C502" s="55"/>
+      <c r="D502" s="55"/>
+      <c r="E502" s="55"/>
+      <c r="F502" s="55"/>
+      <c r="G502" s="55"/>
+      <c r="H502" s="55"/>
+      <c r="I502" s="55"/>
+      <c r="J502" s="55"/>
+      <c r="K502" s="55"/>
+      <c r="L502" s="55"/>
+      <c r="M502" s="55"/>
+      <c r="N502" s="55"/>
+      <c r="O502" s="55"/>
+    </row>
+    <row r="503" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A503" s="55"/>
+      <c r="B503" s="55"/>
+      <c r="C503" s="55"/>
+      <c r="D503" s="55"/>
+      <c r="E503" s="55"/>
+      <c r="F503" s="55"/>
+      <c r="G503" s="55"/>
+      <c r="H503" s="55"/>
+      <c r="I503" s="55"/>
+      <c r="J503" s="55"/>
+      <c r="K503" s="55"/>
+      <c r="L503" s="55"/>
+      <c r="M503" s="55"/>
+      <c r="N503" s="55"/>
+      <c r="O503" s="55"/>
+    </row>
+    <row r="504" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A504" s="55"/>
+      <c r="B504" s="55"/>
+      <c r="C504" s="55"/>
+      <c r="D504" s="55"/>
+      <c r="E504" s="55"/>
+      <c r="F504" s="55"/>
+      <c r="G504" s="55"/>
+      <c r="H504" s="55"/>
+      <c r="I504" s="55"/>
+      <c r="J504" s="55"/>
+      <c r="K504" s="55"/>
+      <c r="L504" s="55"/>
+      <c r="M504" s="55"/>
+      <c r="N504" s="55"/>
+      <c r="O504" s="55"/>
+    </row>
+    <row r="505" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A505" s="55"/>
+      <c r="B505" s="55"/>
+      <c r="C505" s="55"/>
+      <c r="D505" s="55"/>
+      <c r="E505" s="55"/>
+      <c r="F505" s="55"/>
+      <c r="G505" s="55"/>
+      <c r="H505" s="55"/>
+      <c r="I505" s="55"/>
+      <c r="J505" s="55"/>
+      <c r="K505" s="55"/>
+      <c r="L505" s="55"/>
+      <c r="M505" s="55"/>
+      <c r="N505" s="55"/>
+      <c r="O505" s="55"/>
+    </row>
+    <row r="506" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A506" s="55"/>
+      <c r="B506" s="55"/>
+      <c r="C506" s="55"/>
+      <c r="D506" s="55"/>
+      <c r="E506" s="55"/>
+      <c r="F506" s="55"/>
+      <c r="G506" s="55"/>
+      <c r="H506" s="55"/>
+      <c r="I506" s="55"/>
+      <c r="J506" s="55"/>
+      <c r="K506" s="55"/>
+      <c r="L506" s="55"/>
+      <c r="M506" s="55"/>
+      <c r="N506" s="55"/>
+      <c r="O506" s="55"/>
+    </row>
+    <row r="507" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A507" s="55"/>
+      <c r="B507" s="55"/>
+      <c r="C507" s="55"/>
+      <c r="D507" s="55"/>
+      <c r="E507" s="55"/>
+      <c r="F507" s="55"/>
+      <c r="G507" s="55"/>
+      <c r="H507" s="55"/>
+      <c r="I507" s="55"/>
+      <c r="J507" s="55"/>
+      <c r="K507" s="55"/>
+      <c r="L507" s="55"/>
+      <c r="M507" s="55"/>
+      <c r="N507" s="55"/>
+      <c r="O507" s="55"/>
+    </row>
+    <row r="508" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A508" s="55"/>
+      <c r="B508" s="55"/>
+      <c r="C508" s="55"/>
+      <c r="D508" s="55"/>
+      <c r="E508" s="55"/>
+      <c r="F508" s="55"/>
+      <c r="G508" s="55"/>
+      <c r="H508" s="55"/>
+      <c r="I508" s="55"/>
+      <c r="J508" s="55"/>
+      <c r="K508" s="55"/>
+      <c r="L508" s="55"/>
+      <c r="M508" s="55"/>
+      <c r="N508" s="55"/>
+      <c r="O508" s="55"/>
+    </row>
+    <row r="509" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A509" s="55"/>
+      <c r="B509" s="55"/>
+      <c r="C509" s="55"/>
+      <c r="D509" s="55"/>
+      <c r="E509" s="55"/>
+      <c r="F509" s="55"/>
+      <c r="G509" s="55"/>
+      <c r="H509" s="55"/>
+      <c r="I509" s="55"/>
+      <c r="J509" s="55"/>
+      <c r="K509" s="55"/>
+      <c r="L509" s="55"/>
+      <c r="M509" s="55"/>
+      <c r="N509" s="55"/>
+      <c r="O509" s="55"/>
+    </row>
+    <row r="510" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A510" s="55"/>
+      <c r="B510" s="55"/>
+      <c r="C510" s="55"/>
+      <c r="D510" s="55"/>
+      <c r="E510" s="55"/>
+      <c r="F510" s="55"/>
+      <c r="G510" s="55"/>
+      <c r="H510" s="55"/>
+      <c r="I510" s="55"/>
+      <c r="J510" s="55"/>
+      <c r="K510" s="55"/>
+      <c r="L510" s="55"/>
+      <c r="M510" s="55"/>
+      <c r="N510" s="55"/>
+      <c r="O510" s="55"/>
+    </row>
+    <row r="511" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A511" s="55"/>
+      <c r="B511" s="55"/>
+      <c r="C511" s="55"/>
+      <c r="D511" s="55"/>
+      <c r="E511" s="55"/>
+      <c r="F511" s="55"/>
+      <c r="G511" s="55"/>
+      <c r="H511" s="55"/>
+      <c r="I511" s="55"/>
+      <c r="J511" s="55"/>
+      <c r="K511" s="55"/>
+      <c r="L511" s="55"/>
+      <c r="M511" s="55"/>
+      <c r="N511" s="55"/>
+      <c r="O511" s="55"/>
+    </row>
+    <row r="512" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A512" s="55"/>
+      <c r="B512" s="55"/>
+      <c r="C512" s="55"/>
+      <c r="D512" s="55"/>
+      <c r="E512" s="55"/>
+      <c r="F512" s="55"/>
+      <c r="G512" s="55"/>
+      <c r="H512" s="55"/>
+      <c r="I512" s="55"/>
+      <c r="J512" s="55"/>
+      <c r="K512" s="55"/>
+      <c r="L512" s="55"/>
+      <c r="M512" s="55"/>
+      <c r="N512" s="55"/>
+      <c r="O512" s="55"/>
+    </row>
+    <row r="513" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A513" s="55"/>
+      <c r="B513" s="55"/>
+      <c r="C513" s="55"/>
+      <c r="D513" s="55"/>
+      <c r="E513" s="55"/>
+      <c r="F513" s="55"/>
+      <c r="G513" s="55"/>
+      <c r="H513" s="55"/>
+      <c r="I513" s="55"/>
+      <c r="J513" s="55"/>
+      <c r="K513" s="55"/>
+      <c r="L513" s="55"/>
+      <c r="M513" s="55"/>
+      <c r="N513" s="55"/>
+      <c r="O513" s="55"/>
+    </row>
+    <row r="514" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A514" s="55"/>
+      <c r="B514" s="55"/>
+      <c r="C514" s="55"/>
+      <c r="D514" s="55"/>
+      <c r="E514" s="55"/>
+      <c r="F514" s="55"/>
+      <c r="G514" s="55"/>
+      <c r="H514" s="55"/>
+      <c r="I514" s="55"/>
+      <c r="J514" s="55"/>
+      <c r="K514" s="55"/>
+      <c r="L514" s="55"/>
+      <c r="M514" s="55"/>
+      <c r="N514" s="55"/>
+      <c r="O514" s="55"/>
+    </row>
+    <row r="515" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A515" s="55"/>
+      <c r="B515" s="55"/>
+      <c r="C515" s="55"/>
+      <c r="D515" s="55"/>
+      <c r="E515" s="55"/>
+      <c r="F515" s="55"/>
+      <c r="G515" s="55"/>
+      <c r="H515" s="55"/>
+      <c r="I515" s="55"/>
+      <c r="J515" s="55"/>
+      <c r="K515" s="55"/>
+      <c r="L515" s="55"/>
+      <c r="M515" s="55"/>
+      <c r="N515" s="55"/>
+      <c r="O515" s="55"/>
+    </row>
+    <row r="516" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A516" s="55"/>
+      <c r="B516" s="55"/>
+      <c r="C516" s="55"/>
+      <c r="D516" s="55"/>
+      <c r="E516" s="55"/>
+      <c r="F516" s="55"/>
+      <c r="G516" s="55"/>
+      <c r="H516" s="55"/>
+      <c r="I516" s="55"/>
+      <c r="J516" s="55"/>
+      <c r="K516" s="55"/>
+      <c r="L516" s="55"/>
+      <c r="M516" s="55"/>
+      <c r="N516" s="55"/>
+      <c r="O516" s="55"/>
+    </row>
+    <row r="517" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A517" s="55"/>
+      <c r="B517" s="55"/>
+      <c r="C517" s="55"/>
+      <c r="D517" s="55"/>
+      <c r="E517" s="55"/>
+      <c r="F517" s="55"/>
+      <c r="G517" s="55"/>
+      <c r="H517" s="55"/>
+      <c r="I517" s="55"/>
+      <c r="J517" s="55"/>
+      <c r="K517" s="55"/>
+      <c r="L517" s="55"/>
+      <c r="M517" s="55"/>
+      <c r="N517" s="55"/>
+      <c r="O517" s="55"/>
+    </row>
+    <row r="518" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A518" s="55"/>
+      <c r="B518" s="55"/>
+      <c r="C518" s="55"/>
+      <c r="D518" s="55"/>
+      <c r="E518" s="55"/>
+      <c r="F518" s="55"/>
+      <c r="G518" s="55"/>
+      <c r="H518" s="55"/>
+      <c r="I518" s="55"/>
+      <c r="J518" s="55"/>
+      <c r="K518" s="55"/>
+      <c r="L518" s="55"/>
+      <c r="M518" s="55"/>
+      <c r="N518" s="55"/>
+      <c r="O518" s="55"/>
+    </row>
+    <row r="519" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A519" s="55"/>
+      <c r="B519" s="55"/>
+      <c r="C519" s="55"/>
+      <c r="D519" s="55"/>
+      <c r="E519" s="55"/>
+      <c r="F519" s="55"/>
+      <c r="G519" s="55"/>
+      <c r="H519" s="55"/>
+      <c r="I519" s="55"/>
+      <c r="J519" s="55"/>
+      <c r="K519" s="55"/>
+      <c r="L519" s="55"/>
+      <c r="M519" s="55"/>
+      <c r="N519" s="55"/>
+      <c r="O519" s="55"/>
+    </row>
+    <row r="520" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A520" s="55"/>
+      <c r="B520" s="55"/>
+      <c r="C520" s="55"/>
+      <c r="D520" s="55"/>
+      <c r="E520" s="55"/>
+      <c r="F520" s="55"/>
+      <c r="G520" s="55"/>
+      <c r="H520" s="55"/>
+      <c r="I520" s="55"/>
+      <c r="J520" s="55"/>
+      <c r="K520" s="55"/>
+      <c r="L520" s="55"/>
+      <c r="M520" s="55"/>
+      <c r="N520" s="55"/>
+      <c r="O520" s="55"/>
+    </row>
+    <row r="521" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A521" s="55"/>
+      <c r="B521" s="55"/>
+      <c r="C521" s="55"/>
+      <c r="D521" s="55"/>
+      <c r="E521" s="55"/>
+      <c r="F521" s="55"/>
+      <c r="G521" s="55"/>
+      <c r="H521" s="55"/>
+      <c r="I521" s="55"/>
+      <c r="J521" s="55"/>
+      <c r="K521" s="55"/>
+      <c r="L521" s="55"/>
+      <c r="M521" s="55"/>
+      <c r="N521" s="55"/>
+      <c r="O521" s="55"/>
+    </row>
+    <row r="522" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A522" s="55"/>
+      <c r="B522" s="55"/>
+      <c r="C522" s="55"/>
+      <c r="D522" s="55"/>
+      <c r="E522" s="55"/>
+      <c r="F522" s="55"/>
+      <c r="G522" s="55"/>
+      <c r="H522" s="55"/>
+      <c r="I522" s="55"/>
+      <c r="J522" s="55"/>
+      <c r="K522" s="55"/>
+      <c r="L522" s="55"/>
+      <c r="M522" s="55"/>
+      <c r="N522" s="55"/>
+      <c r="O522" s="55"/>
+    </row>
+    <row r="523" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A523" s="55"/>
+      <c r="B523" s="55"/>
+      <c r="C523" s="55"/>
+      <c r="D523" s="55"/>
+      <c r="E523" s="55"/>
+      <c r="F523" s="55"/>
+      <c r="G523" s="55"/>
+      <c r="H523" s="55"/>
+      <c r="I523" s="55"/>
+      <c r="J523" s="55"/>
+      <c r="K523" s="55"/>
+      <c r="L523" s="55"/>
+      <c r="M523" s="55"/>
+      <c r="N523" s="55"/>
+      <c r="O523" s="55"/>
+    </row>
+    <row r="524" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A524" s="55"/>
+      <c r="B524" s="55"/>
+      <c r="C524" s="55"/>
+      <c r="D524" s="55"/>
+      <c r="E524" s="55"/>
+      <c r="F524" s="55"/>
+      <c r="G524" s="55"/>
+      <c r="H524" s="55"/>
+      <c r="I524" s="55"/>
+      <c r="J524" s="55"/>
+      <c r="K524" s="55"/>
+      <c r="L524" s="55"/>
+      <c r="M524" s="55"/>
+      <c r="N524" s="55"/>
+      <c r="O524" s="55"/>
+    </row>
+    <row r="525" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A525" s="55"/>
+      <c r="B525" s="55"/>
+      <c r="C525" s="55"/>
+      <c r="D525" s="55"/>
+      <c r="E525" s="55"/>
+      <c r="F525" s="55"/>
+      <c r="G525" s="55"/>
+      <c r="H525" s="55"/>
+      <c r="I525" s="55"/>
+      <c r="J525" s="55"/>
+      <c r="K525" s="55"/>
+      <c r="L525" s="55"/>
+      <c r="M525" s="55"/>
+      <c r="N525" s="55"/>
+      <c r="O525" s="55"/>
+    </row>
+    <row r="526" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A526" s="55"/>
+      <c r="B526" s="55"/>
+      <c r="C526" s="55"/>
+      <c r="D526" s="55"/>
+      <c r="E526" s="55"/>
+      <c r="F526" s="55"/>
+      <c r="G526" s="55"/>
+      <c r="H526" s="55"/>
+      <c r="I526" s="55"/>
+      <c r="J526" s="55"/>
+      <c r="K526" s="55"/>
+      <c r="L526" s="55"/>
+      <c r="M526" s="55"/>
+      <c r="N526" s="55"/>
+      <c r="O526" s="55"/>
+    </row>
+    <row r="527" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A527" s="55"/>
+      <c r="B527" s="55"/>
+      <c r="C527" s="55"/>
+      <c r="D527" s="55"/>
+      <c r="E527" s="55"/>
+      <c r="F527" s="55"/>
+      <c r="G527" s="55"/>
+      <c r="H527" s="55"/>
+      <c r="I527" s="55"/>
+      <c r="J527" s="55"/>
+      <c r="K527" s="55"/>
+      <c r="L527" s="55"/>
+      <c r="M527" s="55"/>
+      <c r="N527" s="55"/>
+      <c r="O527" s="55"/>
+    </row>
+    <row r="528" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A528" s="55"/>
+      <c r="B528" s="55"/>
+      <c r="C528" s="55"/>
+      <c r="D528" s="55"/>
+      <c r="E528" s="55"/>
+      <c r="F528" s="55"/>
+      <c r="G528" s="55"/>
+      <c r="H528" s="55"/>
+      <c r="I528" s="55"/>
+      <c r="J528" s="55"/>
+      <c r="K528" s="55"/>
+      <c r="L528" s="55"/>
+      <c r="M528" s="55"/>
+      <c r="N528" s="55"/>
+      <c r="O528" s="55"/>
+    </row>
+    <row r="529" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A529" s="55"/>
+      <c r="B529" s="55"/>
+      <c r="C529" s="55"/>
+      <c r="D529" s="55"/>
+      <c r="E529" s="55"/>
+      <c r="F529" s="55"/>
+      <c r="G529" s="55"/>
+      <c r="H529" s="55"/>
+      <c r="I529" s="55"/>
+      <c r="J529" s="55"/>
+      <c r="K529" s="55"/>
+      <c r="L529" s="55"/>
+      <c r="M529" s="55"/>
+      <c r="N529" s="55"/>
+      <c r="O529" s="55"/>
+    </row>
+    <row r="530" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A530" s="55"/>
+      <c r="B530" s="55"/>
+      <c r="C530" s="55"/>
+      <c r="D530" s="55"/>
+      <c r="E530" s="55"/>
+      <c r="F530" s="55"/>
+      <c r="G530" s="55"/>
+      <c r="H530" s="55"/>
+      <c r="I530" s="55"/>
+      <c r="J530" s="55"/>
+      <c r="K530" s="55"/>
+      <c r="L530" s="55"/>
+      <c r="M530" s="55"/>
+      <c r="N530" s="55"/>
+      <c r="O530" s="55"/>
+    </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A531" s="55"/>
+      <c r="B531" s="55"/>
+      <c r="C531" s="55"/>
+      <c r="D531" s="55"/>
+      <c r="E531" s="55"/>
+      <c r="F531" s="55"/>
+      <c r="G531" s="55"/>
+      <c r="H531" s="55"/>
+      <c r="I531" s="55"/>
+      <c r="J531" s="55"/>
+      <c r="K531" s="55"/>
+      <c r="L531" s="55"/>
+      <c r="M531" s="55"/>
+      <c r="N531" s="55"/>
+      <c r="O531" s="55"/>
+    </row>
+    <row r="532" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A532" s="55"/>
+      <c r="B532" s="55"/>
+      <c r="C532" s="55"/>
+      <c r="D532" s="55"/>
+      <c r="E532" s="55"/>
+      <c r="F532" s="55"/>
+      <c r="G532" s="55"/>
+      <c r="H532" s="55"/>
+      <c r="I532" s="55"/>
+      <c r="J532" s="55"/>
+      <c r="K532" s="55"/>
+      <c r="L532" s="55"/>
+      <c r="M532" s="55"/>
+      <c r="N532" s="55"/>
+      <c r="O532" s="55"/>
+    </row>
+    <row r="533" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A533" s="55"/>
+      <c r="B533" s="55"/>
+      <c r="C533" s="55"/>
+      <c r="D533" s="55"/>
+      <c r="E533" s="55"/>
+      <c r="F533" s="55"/>
+      <c r="G533" s="55"/>
+      <c r="H533" s="55"/>
+      <c r="I533" s="55"/>
+      <c r="J533" s="55"/>
+      <c r="K533" s="55"/>
+      <c r="L533" s="55"/>
+      <c r="M533" s="55"/>
+      <c r="N533" s="55"/>
+      <c r="O533" s="55"/>
+    </row>
+    <row r="534" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A534" s="55"/>
+      <c r="B534" s="55"/>
+      <c r="C534" s="55"/>
+      <c r="D534" s="55"/>
+      <c r="E534" s="55"/>
+      <c r="F534" s="55"/>
+      <c r="G534" s="55"/>
+      <c r="H534" s="55"/>
+      <c r="I534" s="55"/>
+      <c r="J534" s="55"/>
+      <c r="K534" s="55"/>
+      <c r="L534" s="55"/>
+      <c r="M534" s="55"/>
+      <c r="N534" s="55"/>
+      <c r="O534" s="55"/>
+    </row>
+    <row r="535" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A535" s="55"/>
+      <c r="B535" s="55"/>
+      <c r="C535" s="55"/>
+      <c r="D535" s="55"/>
+      <c r="E535" s="55"/>
+      <c r="F535" s="55"/>
+      <c r="G535" s="55"/>
+      <c r="H535" s="55"/>
+      <c r="I535" s="55"/>
+      <c r="J535" s="55"/>
+      <c r="K535" s="55"/>
+      <c r="L535" s="55"/>
+      <c r="M535" s="55"/>
+      <c r="N535" s="55"/>
+      <c r="O535" s="55"/>
+    </row>
+    <row r="536" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A536" s="55"/>
+      <c r="B536" s="55"/>
+      <c r="C536" s="55"/>
+      <c r="D536" s="55"/>
+      <c r="E536" s="55"/>
+      <c r="F536" s="55"/>
+      <c r="G536" s="55"/>
+      <c r="H536" s="55"/>
+      <c r="I536" s="55"/>
+      <c r="J536" s="55"/>
+      <c r="K536" s="55"/>
+      <c r="L536" s="55"/>
+      <c r="M536" s="55"/>
+      <c r="N536" s="55"/>
+      <c r="O536" s="55"/>
+    </row>
+    <row r="537" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A537" s="55"/>
+      <c r="B537" s="55"/>
+      <c r="C537" s="55"/>
+      <c r="D537" s="55"/>
+      <c r="E537" s="55"/>
+      <c r="F537" s="55"/>
+      <c r="G537" s="55"/>
+      <c r="H537" s="55"/>
+      <c r="I537" s="55"/>
+      <c r="J537" s="55"/>
+      <c r="K537" s="55"/>
+      <c r="L537" s="55"/>
+      <c r="M537" s="55"/>
+      <c r="N537" s="55"/>
+      <c r="O537" s="55"/>
+    </row>
+    <row r="538" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A538" s="55"/>
+      <c r="B538" s="55"/>
+      <c r="C538" s="55"/>
+      <c r="D538" s="55"/>
+      <c r="E538" s="55"/>
+      <c r="F538" s="55"/>
+      <c r="G538" s="55"/>
+      <c r="H538" s="55"/>
+      <c r="I538" s="55"/>
+      <c r="J538" s="55"/>
+      <c r="K538" s="55"/>
+      <c r="L538" s="55"/>
+      <c r="M538" s="55"/>
+      <c r="N538" s="55"/>
+      <c r="O538" s="55"/>
+    </row>
+    <row r="539" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A539" s="55"/>
+      <c r="B539" s="55"/>
+      <c r="C539" s="55"/>
+      <c r="D539" s="55"/>
+      <c r="E539" s="55"/>
+      <c r="F539" s="55"/>
+      <c r="G539" s="55"/>
+      <c r="H539" s="55"/>
+      <c r="I539" s="55"/>
+      <c r="J539" s="55"/>
+      <c r="K539" s="55"/>
+      <c r="L539" s="55"/>
+      <c r="M539" s="55"/>
+      <c r="N539" s="55"/>
+      <c r="O539" s="55"/>
+    </row>
+    <row r="540" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A540" s="55"/>
+      <c r="B540" s="55"/>
+      <c r="C540" s="55"/>
+      <c r="D540" s="55"/>
+      <c r="E540" s="55"/>
+      <c r="F540" s="55"/>
+      <c r="G540" s="55"/>
+      <c r="H540" s="55"/>
+      <c r="I540" s="55"/>
+      <c r="J540" s="55"/>
+      <c r="K540" s="55"/>
+      <c r="L540" s="55"/>
+      <c r="M540" s="55"/>
+      <c r="N540" s="55"/>
+      <c r="O540" s="55"/>
+    </row>
+    <row r="541" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A541" s="55"/>
+      <c r="B541" s="55"/>
+      <c r="C541" s="55"/>
+      <c r="D541" s="55"/>
+      <c r="E541" s="55"/>
+      <c r="F541" s="55"/>
+      <c r="G541" s="55"/>
+      <c r="H541" s="55"/>
+      <c r="I541" s="55"/>
+      <c r="J541" s="55"/>
+      <c r="K541" s="55"/>
+      <c r="L541" s="55"/>
+      <c r="M541" s="55"/>
+      <c r="N541" s="55"/>
+      <c r="O541" s="55"/>
+    </row>
+    <row r="542" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A542" s="55"/>
+      <c r="B542" s="55"/>
+      <c r="C542" s="55"/>
+      <c r="D542" s="55"/>
+      <c r="E542" s="55"/>
+      <c r="F542" s="55"/>
+      <c r="G542" s="55"/>
+      <c r="H542" s="55"/>
+      <c r="I542" s="55"/>
+      <c r="J542" s="55"/>
+      <c r="K542" s="55"/>
+      <c r="L542" s="55"/>
+      <c r="M542" s="55"/>
+      <c r="N542" s="55"/>
+      <c r="O542" s="55"/>
+    </row>
+    <row r="543" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A543" s="55"/>
+      <c r="B543" s="55"/>
+      <c r="C543" s="55"/>
+      <c r="D543" s="55"/>
+      <c r="E543" s="55"/>
+      <c r="F543" s="55"/>
+      <c r="G543" s="55"/>
+      <c r="H543" s="55"/>
+      <c r="I543" s="55"/>
+      <c r="J543" s="55"/>
+      <c r="K543" s="55"/>
+      <c r="L543" s="55"/>
+      <c r="M543" s="55"/>
+      <c r="N543" s="55"/>
+      <c r="O543" s="55"/>
+    </row>
+    <row r="544" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A544" s="55"/>
+      <c r="B544" s="55"/>
+      <c r="C544" s="55"/>
+      <c r="D544" s="55"/>
+      <c r="E544" s="55"/>
+      <c r="F544" s="55"/>
+      <c r="G544" s="55"/>
+      <c r="H544" s="55"/>
+      <c r="I544" s="55"/>
+      <c r="J544" s="55"/>
+      <c r="K544" s="55"/>
+      <c r="L544" s="55"/>
+      <c r="M544" s="55"/>
+      <c r="N544" s="55"/>
+      <c r="O544" s="55"/>
+    </row>
+    <row r="545" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A545" s="55"/>
+      <c r="B545" s="55"/>
+      <c r="C545" s="55"/>
+      <c r="D545" s="55"/>
+      <c r="E545" s="55"/>
+      <c r="F545" s="55"/>
+      <c r="G545" s="55"/>
+      <c r="H545" s="55"/>
+      <c r="I545" s="55"/>
+      <c r="J545" s="55"/>
+      <c r="K545" s="55"/>
+      <c r="L545" s="55"/>
+      <c r="M545" s="55"/>
+      <c r="N545" s="55"/>
+      <c r="O545" s="55"/>
+    </row>
+    <row r="546" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A546" s="55"/>
+      <c r="B546" s="55"/>
+      <c r="C546" s="55"/>
+      <c r="D546" s="55"/>
+      <c r="E546" s="55"/>
+      <c r="F546" s="55"/>
+      <c r="G546" s="55"/>
+      <c r="H546" s="55"/>
+      <c r="I546" s="55"/>
+      <c r="J546" s="55"/>
+      <c r="K546" s="55"/>
+      <c r="L546" s="55"/>
+      <c r="M546" s="55"/>
+      <c r="N546" s="55"/>
+      <c r="O546" s="55"/>
+    </row>
+    <row r="547" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A547" s="55"/>
+      <c r="B547" s="55"/>
+      <c r="C547" s="55"/>
+      <c r="D547" s="55"/>
+      <c r="E547" s="55"/>
+      <c r="F547" s="55"/>
+      <c r="G547" s="55"/>
+      <c r="H547" s="55"/>
+      <c r="I547" s="55"/>
+      <c r="J547" s="55"/>
+      <c r="K547" s="55"/>
+      <c r="L547" s="55"/>
+      <c r="M547" s="55"/>
+      <c r="N547" s="55"/>
+      <c r="O547" s="55"/>
+    </row>
+    <row r="548" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A548" s="55"/>
+      <c r="B548" s="55"/>
+      <c r="C548" s="55"/>
+      <c r="D548" s="55"/>
+      <c r="E548" s="55"/>
+      <c r="F548" s="55"/>
+      <c r="G548" s="55"/>
+      <c r="H548" s="55"/>
+      <c r="I548" s="55"/>
+      <c r="J548" s="55"/>
+      <c r="K548" s="55"/>
+      <c r="L548" s="55"/>
+      <c r="M548" s="55"/>
+      <c r="N548" s="55"/>
+      <c r="O548" s="55"/>
+    </row>
+    <row r="549" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A549" s="55"/>
+      <c r="B549" s="55"/>
+      <c r="C549" s="55"/>
+      <c r="D549" s="55"/>
+      <c r="E549" s="55"/>
+      <c r="F549" s="55"/>
+      <c r="G549" s="55"/>
+      <c r="H549" s="55"/>
+      <c r="I549" s="55"/>
+      <c r="J549" s="55"/>
+      <c r="K549" s="55"/>
+      <c r="L549" s="55"/>
+      <c r="M549" s="55"/>
+      <c r="N549" s="55"/>
+      <c r="O549" s="55"/>
+    </row>
+    <row r="550" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A550" s="55"/>
+      <c r="B550" s="55"/>
+      <c r="C550" s="55"/>
+      <c r="D550" s="55"/>
+      <c r="E550" s="55"/>
+      <c r="F550" s="55"/>
+      <c r="G550" s="55"/>
+      <c r="H550" s="55"/>
+      <c r="I550" s="55"/>
+      <c r="J550" s="55"/>
+      <c r="K550" s="55"/>
+      <c r="L550" s="55"/>
+      <c r="M550" s="55"/>
+      <c r="N550" s="55"/>
+      <c r="O550" s="55"/>
+    </row>
+    <row r="551" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A551" s="55"/>
+      <c r="B551" s="55"/>
+      <c r="C551" s="55"/>
+      <c r="D551" s="55"/>
+      <c r="E551" s="55"/>
+      <c r="F551" s="55"/>
+      <c r="G551" s="55"/>
+      <c r="H551" s="55"/>
+      <c r="I551" s="55"/>
+      <c r="J551" s="55"/>
+      <c r="K551" s="55"/>
+      <c r="L551" s="55"/>
+      <c r="M551" s="55"/>
+      <c r="N551" s="55"/>
+      <c r="O551" s="55"/>
+    </row>
+    <row r="552" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A552" s="55"/>
+      <c r="B552" s="55"/>
+      <c r="C552" s="55"/>
+      <c r="D552" s="55"/>
+      <c r="E552" s="55"/>
+      <c r="F552" s="55"/>
+      <c r="G552" s="55"/>
+      <c r="H552" s="55"/>
+      <c r="I552" s="55"/>
+      <c r="J552" s="55"/>
+      <c r="K552" s="55"/>
+      <c r="L552" s="55"/>
+      <c r="M552" s="55"/>
+      <c r="N552" s="55"/>
+      <c r="O552" s="55"/>
+    </row>
+    <row r="553" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A553" s="55"/>
+      <c r="B553" s="55"/>
+      <c r="C553" s="55"/>
+      <c r="D553" s="55"/>
+      <c r="E553" s="55"/>
+      <c r="F553" s="55"/>
+      <c r="G553" s="55"/>
+      <c r="H553" s="55"/>
+      <c r="I553" s="55"/>
+      <c r="J553" s="55"/>
+      <c r="K553" s="55"/>
+      <c r="L553" s="55"/>
+      <c r="M553" s="55"/>
+      <c r="N553" s="55"/>
+      <c r="O553" s="55"/>
+    </row>
+    <row r="554" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A554" s="55"/>
+      <c r="B554" s="55"/>
+      <c r="C554" s="55"/>
+      <c r="D554" s="55"/>
+      <c r="E554" s="55"/>
+      <c r="F554" s="55"/>
+      <c r="G554" s="55"/>
+      <c r="H554" s="55"/>
+      <c r="I554" s="55"/>
+      <c r="J554" s="55"/>
+      <c r="K554" s="55"/>
+      <c r="L554" s="55"/>
+      <c r="M554" s="55"/>
+      <c r="N554" s="55"/>
+      <c r="O554" s="55"/>
+    </row>
+    <row r="555" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A555" s="55"/>
+      <c r="B555" s="55"/>
+      <c r="C555" s="55"/>
+      <c r="D555" s="55"/>
+      <c r="E555" s="55"/>
+      <c r="F555" s="55"/>
+      <c r="G555" s="55"/>
+      <c r="H555" s="55"/>
+      <c r="I555" s="55"/>
+      <c r="J555" s="55"/>
+      <c r="K555" s="55"/>
+      <c r="L555" s="55"/>
+      <c r="M555" s="55"/>
+      <c r="N555" s="55"/>
+      <c r="O555" s="55"/>
+    </row>
+    <row r="556" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A556" s="55"/>
+      <c r="B556" s="55"/>
+      <c r="C556" s="55"/>
+      <c r="D556" s="55"/>
+      <c r="E556" s="55"/>
+      <c r="F556" s="55"/>
+      <c r="G556" s="55"/>
+      <c r="H556" s="55"/>
+      <c r="I556" s="55"/>
+      <c r="J556" s="55"/>
+      <c r="K556" s="55"/>
+      <c r="L556" s="55"/>
+      <c r="M556" s="55"/>
+      <c r="N556" s="55"/>
+      <c r="O556" s="55"/>
+    </row>
+    <row r="557" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A557" s="55"/>
+      <c r="B557" s="55"/>
+      <c r="C557" s="55"/>
+      <c r="D557" s="55"/>
+      <c r="E557" s="55"/>
+      <c r="F557" s="55"/>
+      <c r="G557" s="55"/>
+      <c r="H557" s="55"/>
+      <c r="I557" s="55"/>
+      <c r="J557" s="55"/>
+      <c r="K557" s="55"/>
+      <c r="L557" s="55"/>
+      <c r="M557" s="55"/>
+      <c r="N557" s="55"/>
+      <c r="O557" s="55"/>
+    </row>
+    <row r="558" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A558" s="55"/>
+      <c r="B558" s="55"/>
+      <c r="C558" s="55"/>
+      <c r="D558" s="55"/>
+      <c r="E558" s="55"/>
+      <c r="F558" s="55"/>
+      <c r="G558" s="55"/>
+      <c r="H558" s="55"/>
+      <c r="I558" s="55"/>
+      <c r="J558" s="55"/>
+      <c r="K558" s="55"/>
+      <c r="L558" s="55"/>
+      <c r="M558" s="55"/>
+      <c r="N558" s="55"/>
+      <c r="O558" s="55"/>
+    </row>
+    <row r="559" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A559" s="55"/>
+      <c r="B559" s="55"/>
+      <c r="C559" s="55"/>
+      <c r="D559" s="55"/>
+      <c r="E559" s="55"/>
+      <c r="F559" s="55"/>
+      <c r="G559" s="55"/>
+      <c r="H559" s="55"/>
+      <c r="I559" s="55"/>
+      <c r="J559" s="55"/>
+      <c r="K559" s="55"/>
+      <c r="L559" s="55"/>
+      <c r="M559" s="55"/>
+      <c r="N559" s="55"/>
+      <c r="O559" s="55"/>
+    </row>
+    <row r="560" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A560" s="55"/>
+      <c r="B560" s="55"/>
+      <c r="C560" s="55"/>
+      <c r="D560" s="55"/>
+      <c r="E560" s="55"/>
+      <c r="F560" s="55"/>
+      <c r="G560" s="55"/>
+      <c r="H560" s="55"/>
+      <c r="I560" s="55"/>
+      <c r="J560" s="55"/>
+      <c r="K560" s="55"/>
+      <c r="L560" s="55"/>
+      <c r="M560" s="55"/>
+      <c r="N560" s="55"/>
+      <c r="O560" s="55"/>
+    </row>
+    <row r="561" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A561" s="55"/>
+      <c r="B561" s="55"/>
+      <c r="C561" s="55"/>
+      <c r="D561" s="55"/>
+      <c r="E561" s="55"/>
+      <c r="F561" s="55"/>
+      <c r="G561" s="55"/>
+      <c r="H561" s="55"/>
+      <c r="I561" s="55"/>
+      <c r="J561" s="55"/>
+      <c r="K561" s="55"/>
+      <c r="L561" s="55"/>
+      <c r="M561" s="55"/>
+      <c r="N561" s="55"/>
+      <c r="O561" s="55"/>
+    </row>
+    <row r="562" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A562" s="55"/>
+      <c r="B562" s="55"/>
+      <c r="C562" s="55"/>
+      <c r="D562" s="55"/>
+      <c r="E562" s="55"/>
+      <c r="F562" s="55"/>
+      <c r="G562" s="55"/>
+      <c r="H562" s="55"/>
+      <c r="I562" s="55"/>
+      <c r="J562" s="55"/>
+      <c r="K562" s="55"/>
+      <c r="L562" s="55"/>
+      <c r="M562" s="55"/>
+      <c r="N562" s="55"/>
+      <c r="O562" s="55"/>
+    </row>
+    <row r="563" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A563" s="55"/>
+      <c r="B563" s="55"/>
+      <c r="C563" s="55"/>
+      <c r="D563" s="55"/>
+      <c r="E563" s="55"/>
+      <c r="F563" s="55"/>
+      <c r="G563" s="55"/>
+      <c r="H563" s="55"/>
+      <c r="I563" s="55"/>
+      <c r="J563" s="55"/>
+      <c r="K563" s="55"/>
+      <c r="L563" s="55"/>
+      <c r="M563" s="55"/>
+      <c r="N563" s="55"/>
+      <c r="O563" s="55"/>
+    </row>
+    <row r="564" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A564" s="55"/>
+      <c r="B564" s="55"/>
+      <c r="C564" s="55"/>
+      <c r="D564" s="55"/>
+      <c r="E564" s="55"/>
+      <c r="F564" s="55"/>
+      <c r="G564" s="55"/>
+      <c r="H564" s="55"/>
+      <c r="I564" s="55"/>
+      <c r="J564" s="55"/>
+      <c r="K564" s="55"/>
+      <c r="L564" s="55"/>
+      <c r="M564" s="55"/>
+      <c r="N564" s="55"/>
+      <c r="O564" s="55"/>
+    </row>
+    <row r="565" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A565" s="55"/>
+      <c r="B565" s="55"/>
+      <c r="C565" s="55"/>
+      <c r="D565" s="55"/>
+      <c r="E565" s="55"/>
+      <c r="F565" s="55"/>
+      <c r="G565" s="55"/>
+      <c r="H565" s="55"/>
+      <c r="I565" s="55"/>
+      <c r="J565" s="55"/>
+      <c r="K565" s="55"/>
+      <c r="L565" s="55"/>
+      <c r="M565" s="55"/>
+      <c r="N565" s="55"/>
+      <c r="O565" s="55"/>
+    </row>
+    <row r="566" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A566" s="55"/>
+      <c r="B566" s="55"/>
+      <c r="C566" s="55"/>
+      <c r="D566" s="55"/>
+      <c r="E566" s="55"/>
+      <c r="F566" s="55"/>
+      <c r="G566" s="55"/>
+      <c r="H566" s="55"/>
+      <c r="I566" s="55"/>
+      <c r="J566" s="55"/>
+      <c r="K566" s="55"/>
+      <c r="L566" s="55"/>
+      <c r="M566" s="55"/>
+      <c r="N566" s="55"/>
+      <c r="O566" s="55"/>
+    </row>
+    <row r="567" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A567" s="55"/>
+      <c r="B567" s="55"/>
+      <c r="C567" s="55"/>
+      <c r="D567" s="55"/>
+      <c r="E567" s="55"/>
+      <c r="F567" s="55"/>
+      <c r="G567" s="55"/>
+      <c r="H567" s="55"/>
+      <c r="I567" s="55"/>
+      <c r="J567" s="55"/>
+      <c r="K567" s="55"/>
+      <c r="L567" s="55"/>
+      <c r="M567" s="55"/>
+      <c r="N567" s="55"/>
+      <c r="O567" s="55"/>
+    </row>
+    <row r="568" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A568" s="55"/>
+      <c r="B568" s="55"/>
+      <c r="C568" s="55"/>
+      <c r="D568" s="55"/>
+      <c r="E568" s="55"/>
+      <c r="F568" s="55"/>
+      <c r="G568" s="55"/>
+      <c r="H568" s="55"/>
+      <c r="I568" s="55"/>
+      <c r="J568" s="55"/>
+      <c r="K568" s="55"/>
+      <c r="L568" s="55"/>
+      <c r="M568" s="55"/>
+      <c r="N568" s="55"/>
+      <c r="O568" s="55"/>
+    </row>
+    <row r="569" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A569" s="55"/>
+      <c r="B569" s="55"/>
+      <c r="C569" s="55"/>
+      <c r="D569" s="55"/>
+      <c r="E569" s="55"/>
+      <c r="F569" s="55"/>
+      <c r="G569" s="55"/>
+      <c r="H569" s="55"/>
+      <c r="I569" s="55"/>
+      <c r="J569" s="55"/>
+      <c r="K569" s="55"/>
+      <c r="L569" s="55"/>
+      <c r="M569" s="55"/>
+      <c r="N569" s="55"/>
+      <c r="O569" s="55"/>
+    </row>
+    <row r="570" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A570" s="55"/>
+      <c r="B570" s="55"/>
+      <c r="C570" s="55"/>
+      <c r="D570" s="55"/>
+      <c r="E570" s="55"/>
+      <c r="F570" s="55"/>
+      <c r="G570" s="55"/>
+      <c r="H570" s="55"/>
+      <c r="I570" s="55"/>
+      <c r="J570" s="55"/>
+      <c r="K570" s="55"/>
+      <c r="L570" s="55"/>
+      <c r="M570" s="55"/>
+      <c r="N570" s="55"/>
+      <c r="O570" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20313,12 +21973,12 @@
       <c r="M1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="46" t="s">
         <v>202</v>
       </c>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="38"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="48"/>
       <c r="R1" s="24"/>
       <c r="S1" s="24"/>
       <c r="T1" s="24"/>
@@ -23180,44 +24840,44 @@
       <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="39">
+      <c r="A7" s="36">
         <v>1996</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="37">
         <v>45969</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="39">
         <v>0</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="39">
         <v>59</v>
       </c>
-      <c r="F7" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42">
-        <v>1</v>
-      </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="41" t="s">
+      <c r="F7" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39">
+        <v>1</v>
+      </c>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41" t="s">
+      <c r="M7" s="38"/>
+      <c r="N7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="41" t="s">
+      <c r="O7" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="P7" s="43"/>
+      <c r="P7" s="40"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="10">
@@ -23260,168 +24920,168 @@
       <c r="P8" s="9"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="39">
+      <c r="A9" s="36">
         <v>1998</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="37">
         <v>45967</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="39">
         <v>22</v>
       </c>
-      <c r="E9" s="42">
-        <v>6</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="42">
-        <v>1</v>
-      </c>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42" t="s">
+      <c r="E9" s="39">
+        <v>6</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="39">
+        <v>1</v>
+      </c>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41" t="s">
+      <c r="L9" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P9" s="43"/>
+      <c r="P9" s="40"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="39">
+      <c r="A10" s="36">
         <v>1998</v>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="37">
         <v>45974</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="39">
         <v>22</v>
       </c>
-      <c r="E10" s="42">
-        <v>6</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="42">
-        <v>1</v>
-      </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="41" t="s">
+      <c r="E10" s="39">
+        <v>6</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="39">
+        <v>1</v>
+      </c>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41" t="s">
+      <c r="M10" s="38"/>
+      <c r="N10" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="41" t="s">
+      <c r="O10" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="P10" s="43"/>
+      <c r="P10" s="40"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="39">
+      <c r="A11" s="36">
         <v>1998</v>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="37">
         <v>45981</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="42">
-        <v>16</v>
-      </c>
-      <c r="E11" s="42">
+      <c r="D11" s="39">
+        <v>16</v>
+      </c>
+      <c r="E11" s="39">
         <v>15</v>
       </c>
-      <c r="F11" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="42">
-        <v>1</v>
-      </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42" t="s">
+      <c r="F11" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="39">
+        <v>1</v>
+      </c>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="K11" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="41" t="s">
+      <c r="K11" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="M11" s="41" t="s">
+      <c r="M11" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="N11" s="41" t="s">
+      <c r="N11" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="41" t="s">
+      <c r="O11" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="P11" s="43"/>
+      <c r="P11" s="40"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="39">
+      <c r="A12" s="36">
         <v>1998</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="37">
         <v>45988</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="39">
         <v>28</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="39">
         <v>44</v>
       </c>
-      <c r="F12" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42">
-        <v>1</v>
-      </c>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42" t="s">
+      <c r="F12" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39">
+        <v>1</v>
+      </c>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L12" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41" t="s">
+      <c r="L12" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O12" s="41" t="s">
+      <c r="O12" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="43"/>
+      <c r="P12" s="40"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="10">
@@ -23504,124 +25164,124 @@
       <c r="P14" s="9"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="39">
+      <c r="A15" s="36">
         <v>2000</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="37">
         <v>45964</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="39">
         <v>53</v>
       </c>
-      <c r="E15" s="42">
-        <v>16</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="42">
-        <v>1</v>
-      </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42" t="s">
+      <c r="E15" s="39">
+        <v>16</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="39">
+        <v>1</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L15" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41" t="s">
+      <c r="L15" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O15" s="41" t="s">
+      <c r="O15" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P15" s="43"/>
+      <c r="P15" s="40"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="39">
+      <c r="A16" s="36">
         <v>2000</v>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="37">
         <v>45971</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="39">
         <v>14</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="39">
         <v>0</v>
       </c>
-      <c r="F16" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="42">
-        <v>1</v>
-      </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42" t="s">
+      <c r="F16" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="39">
+        <v>1</v>
+      </c>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41" t="s">
+      <c r="L16" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O16" s="41" t="s">
+      <c r="O16" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P16" s="43"/>
+      <c r="P16" s="40"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="39">
+      <c r="A17" s="36">
         <v>2000</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="37">
         <v>45978</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="42">
-        <v>6</v>
-      </c>
-      <c r="E17" s="42">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42">
-        <v>1</v>
-      </c>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42" t="s">
+      <c r="D17" s="39">
+        <v>6</v>
+      </c>
+      <c r="E17" s="39">
+        <v>7</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39">
+        <v>1</v>
+      </c>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L17" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41" t="s">
+      <c r="L17" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O17" s="41" t="s">
+      <c r="O17" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P17" s="43"/>
+      <c r="P17" s="40"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="10">
@@ -23664,86 +25324,86 @@
       <c r="P18" s="9"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="39">
+      <c r="A19" s="36">
         <v>2003</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="37">
         <v>45968</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="39">
         <v>35</v>
       </c>
-      <c r="E19" s="42">
-        <v>7</v>
-      </c>
-      <c r="F19" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="42">
-        <v>1</v>
-      </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42" t="s">
+      <c r="E19" s="39">
+        <v>7</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="39">
+        <v>1</v>
+      </c>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41" t="s">
+      <c r="L19" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O19" s="41" t="s">
+      <c r="O19" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P19" s="43"/>
+      <c r="P19" s="40"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="39">
+      <c r="A20" s="36">
         <v>2003</v>
       </c>
-      <c r="B20" s="40">
+      <c r="B20" s="37">
         <v>45975</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="39">
         <v>14</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="39">
         <v>26</v>
       </c>
-      <c r="F20" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42">
-        <v>1</v>
-      </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="41" t="s">
+      <c r="F20" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39">
+        <v>1</v>
+      </c>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="M20" s="41" t="s">
+      <c r="M20" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="N20" s="41" t="s">
+      <c r="N20" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="O20" s="41" t="s">
+      <c r="O20" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="P20" s="43"/>
+      <c r="P20" s="40"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="10">
@@ -23868,44 +25528,44 @@
       <c r="P23" s="9"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="39">
+      <c r="A24" s="36">
         <v>2006</v>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="37">
         <v>45964</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="42">
-        <v>6</v>
-      </c>
-      <c r="E24" s="42">
+      <c r="D24" s="39">
+        <v>6</v>
+      </c>
+      <c r="E24" s="39">
         <v>35</v>
       </c>
-      <c r="F24" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42">
-        <v>1</v>
-      </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L24" s="41" t="s">
+      <c r="F24" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39">
+        <v>1</v>
+      </c>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41" t="s">
+      <c r="M24" s="38"/>
+      <c r="N24" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O24" s="41" t="s">
+      <c r="O24" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="P24" s="43"/>
+      <c r="P24" s="40"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="10">
@@ -23990,126 +25650,126 @@
       <c r="P26" s="9"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="39">
+      <c r="A27" s="36">
         <v>2008</v>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="37">
         <v>45975</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="39">
         <v>28</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E27" s="39">
         <v>3</v>
       </c>
-      <c r="F27" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="42">
-        <v>1</v>
-      </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42" t="s">
+      <c r="F27" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="39">
+        <v>1</v>
+      </c>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L27" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41" t="s">
+      <c r="L27" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O27" s="41" t="s">
+      <c r="O27" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P27" s="43"/>
+      <c r="P27" s="40"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="39">
+      <c r="A28" s="36">
         <v>2008</v>
       </c>
-      <c r="B28" s="40">
+      <c r="B28" s="37">
         <v>45982</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="39">
         <v>26</v>
       </c>
-      <c r="E28" s="42">
+      <c r="E28" s="39">
         <v>20</v>
       </c>
-      <c r="F28" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="42">
-        <v>1</v>
-      </c>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L28" s="41" t="s">
+      <c r="F28" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="39">
+        <v>1</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L28" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41" t="s">
+      <c r="M28" s="38"/>
+      <c r="N28" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O28" s="41" t="s">
+      <c r="O28" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="P28" s="43"/>
+      <c r="P28" s="40"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="39">
+      <c r="A29" s="36">
         <v>2008</v>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="37">
         <v>45989</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="39">
         <v>8</v>
       </c>
-      <c r="E29" s="42">
+      <c r="E29" s="39">
         <v>35</v>
       </c>
-      <c r="F29" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42">
-        <v>1</v>
-      </c>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L29" s="41" t="s">
+      <c r="F29" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39">
+        <v>1</v>
+      </c>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L29" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="M29" s="41" t="s">
+      <c r="M29" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="N29" s="41" t="s">
+      <c r="N29" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O29" s="41" t="s">
+      <c r="O29" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="P29" s="43"/>
+      <c r="P29" s="40"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="10">
@@ -24276,84 +25936,84 @@
       <c r="P33" s="9"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="39">
+      <c r="A34" s="36">
         <v>2010</v>
       </c>
-      <c r="B34" s="40">
+      <c r="B34" s="37">
         <v>45966</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="42">
+      <c r="D34" s="39">
         <v>47</v>
       </c>
-      <c r="E34" s="42">
+      <c r="E34" s="39">
         <v>20</v>
       </c>
-      <c r="F34" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="42">
-        <v>1</v>
-      </c>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42" t="s">
+      <c r="F34" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="39">
+        <v>1</v>
+      </c>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L34" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41" t="s">
+      <c r="L34" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O34" s="41" t="s">
+      <c r="O34" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P34" s="43"/>
+      <c r="P34" s="40"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="39">
+      <c r="A35" s="36">
         <v>2010</v>
       </c>
-      <c r="B35" s="40">
+      <c r="B35" s="37">
         <v>45973</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C35" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="39">
         <v>12</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="39">
         <v>15</v>
       </c>
-      <c r="F35" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42">
-        <v>1</v>
-      </c>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42" t="s">
+      <c r="F35" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39">
+        <v>1</v>
+      </c>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L35" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41" t="s">
+      <c r="L35" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O35" s="41" t="s">
+      <c r="O35" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="P35" s="43"/>
+      <c r="P35" s="40"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="10">
@@ -24396,44 +26056,44 @@
       <c r="P36" s="9"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="39">
+      <c r="A37" s="36">
         <v>2012</v>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="37">
         <v>45963</v>
       </c>
-      <c r="C37" s="41" t="s">
+      <c r="C37" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="42">
+      <c r="D37" s="39">
         <v>14</v>
       </c>
-      <c r="E37" s="42">
+      <c r="E37" s="39">
         <v>59</v>
       </c>
-      <c r="F37" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42">
-        <v>1</v>
-      </c>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L37" s="41" t="s">
+      <c r="F37" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39">
+        <v>1</v>
+      </c>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="M37" s="41"/>
-      <c r="N37" s="41" t="s">
+      <c r="M37" s="38"/>
+      <c r="N37" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O37" s="41" t="s">
+      <c r="O37" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="P37" s="43"/>
+      <c r="P37" s="40"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="10">
@@ -24476,44 +26136,44 @@
       <c r="P38" s="9"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="39">
+      <c r="A39" s="36">
         <v>2014</v>
       </c>
-      <c r="B39" s="40">
+      <c r="B39" s="37">
         <v>45968</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C39" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="42">
+      <c r="D39" s="39">
         <v>26</v>
       </c>
-      <c r="E39" s="42">
+      <c r="E39" s="39">
         <v>34</v>
       </c>
-      <c r="F39" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42">
-        <v>1</v>
-      </c>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L39" s="41" t="s">
+      <c r="F39" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39">
+        <v>1</v>
+      </c>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L39" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41" t="s">
+      <c r="M39" s="38"/>
+      <c r="N39" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="O39" s="41" t="s">
+      <c r="O39" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="P39" s="43"/>
+      <c r="P39" s="40"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="10">
@@ -24556,46 +26216,46 @@
       <c r="P40" s="9"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="39">
+      <c r="A41" s="36">
         <v>2019</v>
       </c>
-      <c r="B41" s="40">
+      <c r="B41" s="37">
         <v>45969</v>
       </c>
-      <c r="C41" s="41" t="s">
+      <c r="C41" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="42">
+      <c r="D41" s="39">
         <v>24</v>
       </c>
-      <c r="E41" s="42">
+      <c r="E41" s="39">
         <v>41</v>
       </c>
-      <c r="F41" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42">
-        <v>1</v>
-      </c>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
-      <c r="K41" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L41" s="41" t="s">
+      <c r="F41" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39">
+        <v>1</v>
+      </c>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="M41" s="41" t="s">
+      <c r="M41" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="N41" s="41" t="s">
+      <c r="N41" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="O41" s="41" t="s">
+      <c r="O41" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="P41" s="43"/>
+      <c r="P41" s="40"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="10">
@@ -25071,10 +26731,10 @@
       <c r="A54" s="14"/>
       <c r="B54" s="17"/>
       <c r="C54" s="16"/>
-      <c r="D54" s="44">
+      <c r="D54" s="41">
         <v>1094</v>
       </c>
-      <c r="E54" s="44">
+      <c r="E54" s="41">
         <v>1269</v>
       </c>
       <c r="F54" s="17"/>
@@ -25098,27 +26758,27 @@
       <c r="P54" s="18"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="45"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="46">
+      <c r="A55" s="42"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="43">
         <v>21.45</v>
       </c>
-      <c r="E55" s="46">
+      <c r="E55" s="43">
         <v>24.88</v>
       </c>
-      <c r="F55" s="48">
+      <c r="F55" s="45">
         <v>-3.43</v>
       </c>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="47"/>
-      <c r="M55" s="47"/>
-      <c r="N55" s="47"/>
-      <c r="O55" s="47"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+      <c r="L55" s="44"/>
+      <c r="M55" s="44"/>
+      <c r="N55" s="44"/>
+      <c r="O55" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
